--- a/data/dental_laboratories/data.xlsx
+++ b/data/dental_laboratories/data.xlsx
@@ -1988,7 +1988,7 @@
         <v>香川県高松市太田上町７８０番地４</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>2015/4/1</v>
       </c>
       <c r="I55" t="str">
         <v/>

--- a/data/dental_laboratories/data.xlsx
+++ b/data/dental_laboratories/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\itfile01\保健医療政策課\オープンデータ\歯科技工所（0116）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userdata\52845\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CF1A22-78CD-4B3C-8C68-99F744302FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36675EB-6924-49F9-B30A-48DAC0B324E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="11652" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="575">
   <si>
     <t>№</t>
   </si>
@@ -88,6 +88,9 @@
     <t>134.082306</t>
   </si>
   <si>
+    <t>高松市由良町１２２９番地３９</t>
+  </si>
+  <si>
     <t>1999/1/23</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>134.082303</t>
   </si>
   <si>
+    <t>高松市屋島西町２３０４番地１１</t>
+  </si>
+  <si>
     <t>1986/3/25</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
     <t>134.042311</t>
   </si>
   <si>
+    <t>高松市太田上町９５０番地８</t>
+  </si>
+  <si>
     <t>1987/2/1</t>
   </si>
   <si>
@@ -142,6 +151,9 @@
     <t>134.089535</t>
   </si>
   <si>
+    <t>高松市屋島西町２３０４番地１０</t>
+  </si>
+  <si>
     <t>1990/12/4</t>
   </si>
   <si>
@@ -160,6 +172,9 @@
     <t>134.047391</t>
   </si>
   <si>
+    <t>高松市三条町２９９番地８</t>
+  </si>
+  <si>
     <t>1974/5/1</t>
   </si>
   <si>
@@ -199,6 +214,9 @@
     <t>134.011987</t>
   </si>
   <si>
+    <t>高松市鶴市町２０３５番地４</t>
+  </si>
+  <si>
     <t>1988/12/1</t>
   </si>
   <si>
@@ -217,6 +235,9 @@
     <t>134.012909</t>
   </si>
   <si>
+    <t>高松市郷東町４９６番地</t>
+  </si>
+  <si>
     <t>1991/6/4</t>
   </si>
   <si>
@@ -235,6 +256,9 @@
     <t>134.089711</t>
   </si>
   <si>
+    <t>高松市由良町２９９番地６</t>
+  </si>
+  <si>
     <t>1992/5/1</t>
   </si>
   <si>
@@ -274,6 +298,9 @@
     <t>134.089064</t>
   </si>
   <si>
+    <t>高松市春日町４１２番地５</t>
+  </si>
+  <si>
     <t>1994/2/14</t>
   </si>
   <si>
@@ -292,6 +319,9 @@
     <t>134.078517</t>
   </si>
   <si>
+    <t>高松市木太町３１６４番地１３</t>
+  </si>
+  <si>
     <t>1995/4/14</t>
   </si>
   <si>
@@ -310,6 +340,9 @@
     <t>134.069966</t>
   </si>
   <si>
+    <t>高松市松島町三丁目１５番１２号</t>
+  </si>
+  <si>
     <t>1981/4/1</t>
   </si>
   <si>
@@ -328,6 +361,9 @@
     <t>133.996525</t>
   </si>
   <si>
+    <t>高松市飯田町４２３番地５</t>
+  </si>
+  <si>
     <t>1994/7/14</t>
   </si>
   <si>
@@ -346,6 +382,9 @@
     <t>134.036108</t>
   </si>
   <si>
+    <t>高松市宮脇町二丁目２５番１号</t>
+  </si>
+  <si>
     <t>1997/8/21</t>
   </si>
   <si>
@@ -364,6 +403,9 @@
     <t>134.036098</t>
   </si>
   <si>
+    <t>高松市木太町２９０５番地９</t>
+  </si>
+  <si>
     <t>1997/10/1</t>
   </si>
   <si>
@@ -382,6 +424,9 @@
     <t>134.060114</t>
   </si>
   <si>
+    <t>高松市松縄町１０２０番地１</t>
+  </si>
+  <si>
     <t>1998/1/1</t>
   </si>
   <si>
@@ -400,6 +445,9 @@
     <t>134.046701</t>
   </si>
   <si>
+    <t>高松市中央町１番６号</t>
+  </si>
+  <si>
     <t>1999/5/1</t>
   </si>
   <si>
@@ -418,6 +466,9 @@
     <t>134.080606</t>
   </si>
   <si>
+    <t>高松市川島本町５４８番地８</t>
+  </si>
+  <si>
     <t>2000/1/1</t>
   </si>
   <si>
@@ -436,6 +487,9 @@
     <t>134.050282</t>
   </si>
   <si>
+    <t>高松市仏生山町乙８１番地２</t>
+  </si>
+  <si>
     <t>2001/2/1</t>
   </si>
   <si>
@@ -454,6 +508,9 @@
     <t>134.101423</t>
   </si>
   <si>
+    <t>高松市前田西町１０７４番地</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
@@ -469,6 +526,9 @@
     <t>134.101445</t>
   </si>
   <si>
+    <t>高松市高松町１４９３番地３</t>
+  </si>
+  <si>
     <t>1985/8/1</t>
   </si>
   <si>
@@ -487,6 +547,9 @@
     <t>134.090701</t>
   </si>
   <si>
+    <t>高松市東山崎町６８１番地５</t>
+  </si>
+  <si>
     <t>1995/8/21</t>
   </si>
   <si>
@@ -505,27 +568,12 @@
     <t>134.089773</t>
   </si>
   <si>
+    <t>高松市屋島西町２３００番地１８</t>
+  </si>
+  <si>
     <t>1991/1/1</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>是本歯科技工所</t>
-  </si>
-  <si>
-    <t>是本　政廣</t>
-  </si>
-  <si>
-    <t>34.354748</t>
-  </si>
-  <si>
-    <t>134.089751</t>
-  </si>
-  <si>
-    <t>1985/1/0</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -541,6 +589,9 @@
     <t>133.985708</t>
   </si>
   <si>
+    <t>高松市香西北町６６０番地３</t>
+  </si>
+  <si>
     <t>2003/1/1</t>
   </si>
   <si>
@@ -559,6 +610,9 @@
     <t>134.040022</t>
   </si>
   <si>
+    <t>高松市太田上町３１９番地１</t>
+  </si>
+  <si>
     <t>2005/6/1</t>
   </si>
   <si>
@@ -577,6 +631,9 @@
     <t>133.945764</t>
   </si>
   <si>
+    <t>高松市国分寺町国分２１１９番地１０</t>
+  </si>
+  <si>
     <t>1994/4/3</t>
   </si>
   <si>
@@ -595,6 +652,9 @@
     <t>133.945769</t>
   </si>
   <si>
+    <t>高松市国分寺町新居３１８０番地</t>
+  </si>
+  <si>
     <t>31</t>
   </si>
   <si>
@@ -610,6 +670,9 @@
     <t>133.969189</t>
   </si>
   <si>
+    <t>高松市国分寺町福家甲３９７１番地１</t>
+  </si>
+  <si>
     <t>2004/10/6</t>
   </si>
   <si>
@@ -628,6 +691,9 @@
     <t>134.011841</t>
   </si>
   <si>
+    <t>高松市香南町吉光１４４番地５</t>
+  </si>
+  <si>
     <t>1986/1/5</t>
   </si>
   <si>
@@ -646,6 +712,9 @@
     <t>134.011067</t>
   </si>
   <si>
+    <t>高松市香南町吉光１３７番地５</t>
+  </si>
+  <si>
     <t>2008/3/3</t>
   </si>
   <si>
@@ -664,6 +733,9 @@
     <t>134.126576</t>
   </si>
   <si>
+    <t>高松市牟礼町牟礼３０１３番地１</t>
+  </si>
+  <si>
     <t>2000/5/23</t>
   </si>
   <si>
@@ -682,6 +754,9 @@
     <t>134.035301</t>
   </si>
   <si>
+    <t>高松市香川町浅野２６５番地３</t>
+  </si>
+  <si>
     <t>2002/8/8</t>
   </si>
   <si>
@@ -700,6 +775,9 @@
     <t>134.116159</t>
   </si>
   <si>
+    <t>高松市亀田町２９５番地１０</t>
+  </si>
+  <si>
     <t>2006/4/1</t>
   </si>
   <si>
@@ -718,6 +796,9 @@
     <t>134.121481</t>
   </si>
   <si>
+    <t>高松市前田東町３６３番地３</t>
+  </si>
+  <si>
     <t>1994/9/1</t>
   </si>
   <si>
@@ -736,6 +817,9 @@
     <t>133.947742</t>
   </si>
   <si>
+    <t>高松市国分寺町国分８４５番地１</t>
+  </si>
+  <si>
     <t>2007/2/13</t>
   </si>
   <si>
@@ -754,6 +838,9 @@
     <t>133.968828</t>
   </si>
   <si>
+    <t>高松市国分寺町新居３９６番地１</t>
+  </si>
+  <si>
     <t>2007/2/17</t>
   </si>
   <si>
@@ -772,6 +859,9 @@
     <t>133.988281</t>
   </si>
   <si>
+    <t>高松市中間町１２３４番地</t>
+  </si>
+  <si>
     <t>2007/6/27</t>
   </si>
   <si>
@@ -790,6 +880,9 @@
     <t>134.077587</t>
   </si>
   <si>
+    <t>高松市林町３６４番地６</t>
+  </si>
+  <si>
     <t>2008/3/1</t>
   </si>
   <si>
@@ -808,6 +901,9 @@
     <t>134.003924</t>
   </si>
   <si>
+    <t>高松市香西本町６６番地３</t>
+  </si>
+  <si>
     <t>2008/9/3</t>
   </si>
   <si>
@@ -826,6 +922,9 @@
     <t>134.112117</t>
   </si>
   <si>
+    <t>高松市前田西町５５０番地</t>
+  </si>
+  <si>
     <t>2009/4/1</t>
   </si>
   <si>
@@ -844,6 +943,9 @@
     <t>134.092037</t>
   </si>
   <si>
+    <t>高松市川島東町１２４９番地１１</t>
+  </si>
+  <si>
     <t>1988/2/1</t>
   </si>
   <si>
@@ -865,6 +967,9 @@
     <t>134.087783</t>
   </si>
   <si>
+    <t>高松市川島東町９５２番地２５</t>
+  </si>
+  <si>
     <t>2000/2/26</t>
   </si>
   <si>
@@ -883,6 +988,9 @@
     <t>134.038219</t>
   </si>
   <si>
+    <t>高松市仏生山町甲１９２２番地４</t>
+  </si>
+  <si>
     <t>2012/4/21</t>
   </si>
   <si>
@@ -901,6 +1009,9 @@
     <t>134.079851</t>
   </si>
   <si>
+    <t>高松市木太町３６１１−1</t>
+  </si>
+  <si>
     <t>2020/4/1</t>
   </si>
   <si>
@@ -919,6 +1030,9 @@
     <t>134.054186</t>
   </si>
   <si>
+    <t>高松市多肥上町１２２３番地１９</t>
+  </si>
+  <si>
     <t>2026/7/3</t>
   </si>
   <si>
@@ -937,6 +1051,9 @@
     <t>133.959358</t>
   </si>
   <si>
+    <t>高松市国分寺町新居１７６１番地１・国分寺町新居３３８１番地１</t>
+  </si>
+  <si>
     <t>2013/2/1</t>
   </si>
   <si>
@@ -955,6 +1072,9 @@
     <t>134.050731</t>
   </si>
   <si>
+    <t>高松市藤塚町二丁目４番８号</t>
+  </si>
+  <si>
     <t>2014/2/4</t>
   </si>
   <si>
@@ -973,6 +1093,9 @@
     <t>134.058741</t>
   </si>
   <si>
+    <t>高松市多賀町二丁目９番２７号</t>
+  </si>
+  <si>
     <t>2014/5/7</t>
   </si>
   <si>
@@ -991,6 +1114,9 @@
     <t>133.98905</t>
   </si>
   <si>
+    <t>高松市鬼無町佐藤５７２番地</t>
+  </si>
+  <si>
     <t>2014/11/21</t>
   </si>
   <si>
@@ -1009,6 +1135,9 @@
     <t>134.069946</t>
   </si>
   <si>
+    <t>高松市林町２０２番地１５</t>
+  </si>
+  <si>
     <t>1900/1/0</t>
   </si>
   <si>
@@ -1027,6 +1156,9 @@
     <t>134.046789</t>
   </si>
   <si>
+    <t>高松市太田上町７８０番地４</t>
+  </si>
+  <si>
     <t>2015/4/1</t>
   </si>
   <si>
@@ -1045,6 +1177,9 @@
     <t>134.008167</t>
   </si>
   <si>
+    <t>高松市鶴市町６６６番地６２　２Ｆ</t>
+  </si>
+  <si>
     <t>1998/4/1</t>
   </si>
   <si>
@@ -1063,6 +1198,9 @@
     <t>134.031271</t>
   </si>
   <si>
+    <t>高松市西ハゼ町１８８番地１　三笠ハイツ１０２</t>
+  </si>
+  <si>
     <t>2015/5/18</t>
   </si>
   <si>
@@ -1084,6 +1222,9 @@
     <t>134.042798</t>
   </si>
   <si>
+    <t>高松市錦町二丁目８番３８号</t>
+  </si>
+  <si>
     <t>2015/7/27</t>
   </si>
   <si>
@@ -1102,6 +1243,9 @@
     <t>134.105116</t>
   </si>
   <si>
+    <t>高松市十川東町６５６番地３</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
@@ -1117,6 +1261,9 @@
     <t>134.056046</t>
   </si>
   <si>
+    <t>高松市今里町一丁目４５４番地１</t>
+  </si>
+  <si>
     <t>2015/9/26</t>
   </si>
   <si>
@@ -1135,6 +1282,9 @@
     <t>134.103712</t>
   </si>
   <si>
+    <t>高松市新田町甲６３３番地１</t>
+  </si>
+  <si>
     <t>2009/2/1</t>
   </si>
   <si>
@@ -1153,6 +1303,9 @@
     <t>134.054351</t>
   </si>
   <si>
+    <t>高松市伏石町２０１４番地４</t>
+  </si>
+  <si>
     <t>2017/1/1</t>
   </si>
   <si>
@@ -1171,6 +1324,9 @@
     <t>134.021864</t>
   </si>
   <si>
+    <t>高松市勅使町１４１０番地４−３</t>
+  </si>
+  <si>
     <t>2018/11/29</t>
   </si>
   <si>
@@ -1189,6 +1345,9 @@
     <t>134.054181</t>
   </si>
   <si>
+    <t>高松市三谷町４３６７番地９</t>
+  </si>
+  <si>
     <t>2016/4/6</t>
   </si>
   <si>
@@ -1207,6 +1366,9 @@
     <t>134.047348</t>
   </si>
   <si>
+    <t>高松市仏生山町甲４３７番地１</t>
+  </si>
+  <si>
     <t>2019/1/21</t>
   </si>
   <si>
@@ -1225,6 +1387,9 @@
     <t>134.041642</t>
   </si>
   <si>
+    <t>高松市太田上町９７８番地８</t>
+  </si>
+  <si>
     <t>2019/4/15</t>
   </si>
   <si>
@@ -1243,6 +1408,9 @@
     <t>134.054401</t>
   </si>
   <si>
+    <t>高松市三谷町４３９１番地１</t>
+  </si>
+  <si>
     <t>2019/8/16</t>
   </si>
   <si>
@@ -1261,6 +1429,9 @@
     <t>134.024878</t>
   </si>
   <si>
+    <t>高松市西町１９番３号</t>
+  </si>
+  <si>
     <t>2019/11/7</t>
   </si>
   <si>
@@ -1282,6 +1453,9 @@
     <t>134.068643</t>
   </si>
   <si>
+    <t>高松市上林町字竹部６５番地１</t>
+  </si>
+  <si>
     <t>2019/4/1</t>
   </si>
   <si>
@@ -1300,6 +1474,9 @@
     <t>134.103721</t>
   </si>
   <si>
+    <t>高松市十川西町５１４番地１４</t>
+  </si>
+  <si>
     <t>2020/9/2</t>
   </si>
   <si>
@@ -1318,6 +1495,9 @@
     <t>134.053913</t>
   </si>
   <si>
+    <t>高松市多肥上町６３０番地４</t>
+  </si>
+  <si>
     <t>2021/1/4</t>
   </si>
   <si>
@@ -1336,6 +1516,9 @@
     <t>134.057481</t>
   </si>
   <si>
+    <t>高松市多肥上町字松林１２９２番地１</t>
+  </si>
+  <si>
     <t>2021/12/1</t>
   </si>
   <si>
@@ -1354,6 +1537,9 @@
     <t>134.004085</t>
   </si>
   <si>
+    <t>高松市香西本町５０番地５　アドバンス香西Ｂ棟１０２</t>
+  </si>
+  <si>
     <t>2022/5/1</t>
   </si>
   <si>
@@ -1372,6 +1558,9 @@
     <t>134.031176</t>
   </si>
   <si>
+    <t>高松市香川町川東上１４３６番地１</t>
+  </si>
+  <si>
     <t>2022/9/28</t>
   </si>
   <si>
@@ -1393,6 +1582,9 @@
     <t>134.005401</t>
   </si>
   <si>
+    <t>高松市香西東町３１５番地10</t>
+  </si>
+  <si>
     <t>2023/1/10</t>
   </si>
   <si>
@@ -1411,6 +1603,9 @@
     <t>134.043396</t>
   </si>
   <si>
+    <t>高松市仏生山町甲３２３番地</t>
+  </si>
+  <si>
     <t>1993/5/1</t>
   </si>
   <si>
@@ -1429,6 +1624,9 @@
     <t>134.130906</t>
   </si>
   <si>
+    <t>高松市庵治町５４５５番地１</t>
+  </si>
+  <si>
     <t>2023/4/8</t>
   </si>
   <si>
@@ -1447,6 +1645,9 @@
     <t>134.117562</t>
   </si>
   <si>
+    <t>高松市高松町１４６４番地１３</t>
+  </si>
+  <si>
     <t>2024/10/1</t>
   </si>
   <si>
@@ -1465,6 +1666,9 @@
     <t>134.103766</t>
   </si>
   <si>
+    <t>高松市新田町甲６１４番地８</t>
+  </si>
+  <si>
     <t>2024/3/21</t>
   </si>
   <si>
@@ -1480,6 +1684,9 @@
     <t>134.072305</t>
   </si>
   <si>
+    <t>高松市木太町２３３６番地１</t>
+  </si>
+  <si>
     <t>2024/9/27</t>
   </si>
   <si>
@@ -1538,234 +1745,6 @@
   </si>
   <si>
     <t>2025/12/15</t>
-  </si>
-  <si>
-    <t>高松市由良町１２２９番地３９</t>
-  </si>
-  <si>
-    <t>高松市屋島西町２３０４番地１１</t>
-  </si>
-  <si>
-    <t>高松市太田上町９５０番地８</t>
-  </si>
-  <si>
-    <t>高松市屋島西町２３０４番地１０</t>
-  </si>
-  <si>
-    <t>高松市三条町２９９番地８</t>
-  </si>
-  <si>
-    <t>高松市鶴市町２０３５番地４</t>
-  </si>
-  <si>
-    <t>高松市郷東町４９６番地</t>
-  </si>
-  <si>
-    <t>高松市由良町２９９番地６</t>
-  </si>
-  <si>
-    <t>高松市春日町４１２番地５</t>
-  </si>
-  <si>
-    <t>高松市木太町３１６４番地１３</t>
-  </si>
-  <si>
-    <t>高松市松島町三丁目１５番１２号</t>
-  </si>
-  <si>
-    <t>高松市飯田町４２３番地５</t>
-  </si>
-  <si>
-    <t>高松市宮脇町二丁目２５番１号</t>
-  </si>
-  <si>
-    <t>高松市木太町２９０５番地９</t>
-  </si>
-  <si>
-    <t>高松市松縄町１０２０番地１</t>
-  </si>
-  <si>
-    <t>高松市中央町１番６号</t>
-  </si>
-  <si>
-    <t>高松市川島本町５４８番地８</t>
-  </si>
-  <si>
-    <t>高松市仏生山町乙８１番地２</t>
-  </si>
-  <si>
-    <t>高松市前田西町１０７４番地</t>
-  </si>
-  <si>
-    <t>高松市高松町１４９３番地３</t>
-  </si>
-  <si>
-    <t>高松市東山崎町６８１番地５</t>
-  </si>
-  <si>
-    <t>高松市屋島西町２３００番地１８</t>
-  </si>
-  <si>
-    <t>高松市亀水町８０７番地２</t>
-  </si>
-  <si>
-    <t>高松市香西北町６６０番地３</t>
-  </si>
-  <si>
-    <t>高松市太田上町３１９番地１</t>
-  </si>
-  <si>
-    <t>高松市国分寺町国分２１１９番地１０</t>
-  </si>
-  <si>
-    <t>高松市国分寺町新居３１８０番地</t>
-  </si>
-  <si>
-    <t>高松市国分寺町福家甲３９７１番地１</t>
-  </si>
-  <si>
-    <t>高松市香南町吉光１４４番地５</t>
-  </si>
-  <si>
-    <t>高松市香南町吉光１３７番地５</t>
-  </si>
-  <si>
-    <t>高松市牟礼町牟礼３０１３番地１</t>
-  </si>
-  <si>
-    <t>高松市香川町浅野２６５番地３</t>
-  </si>
-  <si>
-    <t>高松市亀田町２９５番地１０</t>
-  </si>
-  <si>
-    <t>高松市前田東町３６３番地３</t>
-  </si>
-  <si>
-    <t>高松市国分寺町国分８４５番地１</t>
-  </si>
-  <si>
-    <t>高松市国分寺町新居３９６番地１</t>
-  </si>
-  <si>
-    <t>高松市中間町１２３４番地</t>
-  </si>
-  <si>
-    <t>高松市林町３６４番地６</t>
-  </si>
-  <si>
-    <t>高松市香西本町６６番地３</t>
-  </si>
-  <si>
-    <t>高松市前田西町５５０番地</t>
-  </si>
-  <si>
-    <t>高松市川島東町１２４９番地１１</t>
-  </si>
-  <si>
-    <t>高松市川島東町９５２番地２５</t>
-  </si>
-  <si>
-    <t>高松市仏生山町甲１９２２番地４</t>
-  </si>
-  <si>
-    <t>高松市木太町３６１１−1</t>
-  </si>
-  <si>
-    <t>高松市多肥上町１２２３番地１９</t>
-  </si>
-  <si>
-    <t>高松市国分寺町新居１７６１番地１・国分寺町新居３３８１番地１</t>
-  </si>
-  <si>
-    <t>高松市藤塚町二丁目４番８号</t>
-  </si>
-  <si>
-    <t>高松市多賀町二丁目９番２７号</t>
-  </si>
-  <si>
-    <t>高松市鬼無町佐藤５７２番地</t>
-  </si>
-  <si>
-    <t>高松市林町２０２番地１５</t>
-  </si>
-  <si>
-    <t>高松市太田上町７８０番地４</t>
-  </si>
-  <si>
-    <t>高松市鶴市町６６６番地６２　２Ｆ</t>
-  </si>
-  <si>
-    <t>高松市西ハゼ町１８８番地１　三笠ハイツ１０２</t>
-  </si>
-  <si>
-    <t>高松市錦町二丁目８番３８号</t>
-  </si>
-  <si>
-    <t>高松市十川東町６５６番地３</t>
-  </si>
-  <si>
-    <t>高松市今里町一丁目４５４番地１</t>
-  </si>
-  <si>
-    <t>高松市新田町甲６３３番地１</t>
-  </si>
-  <si>
-    <t>高松市伏石町２０１４番地４</t>
-  </si>
-  <si>
-    <t>高松市勅使町１４１０番地４−３</t>
-  </si>
-  <si>
-    <t>高松市三谷町４３６７番地９</t>
-  </si>
-  <si>
-    <t>高松市仏生山町甲４３７番地１</t>
-  </si>
-  <si>
-    <t>高松市太田上町９７８番地８</t>
-  </si>
-  <si>
-    <t>高松市三谷町４３９１番地１</t>
-  </si>
-  <si>
-    <t>高松市西町１９番３号</t>
-  </si>
-  <si>
-    <t>高松市上林町字竹部６５番地１</t>
-  </si>
-  <si>
-    <t>高松市十川西町５１４番地１４</t>
-  </si>
-  <si>
-    <t>高松市多肥上町６３０番地４</t>
-  </si>
-  <si>
-    <t>高松市多肥上町字松林１２９２番地１</t>
-  </si>
-  <si>
-    <t>高松市香西本町５０番地５　アドバンス香西Ｂ棟１０２</t>
-  </si>
-  <si>
-    <t>高松市香川町川東上１４３６番地１</t>
-  </si>
-  <si>
-    <t>高松市香西東町３１５番地10</t>
-  </si>
-  <si>
-    <t>高松市仏生山町甲３２３番地</t>
-  </si>
-  <si>
-    <t>高松市庵治町５４５５番地１</t>
-  </si>
-  <si>
-    <t>高松市高松町１４６４番地１３</t>
-  </si>
-  <si>
-    <t>高松市新田町甲６１４番地８</t>
-  </si>
-  <si>
-    <t>高松市木太町２３３６番地１</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1788,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2149,11 +2128,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="7" max="7" width="64.796875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2233,10 +2209,10 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>506</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -2244,28 +2220,28 @@
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>507</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -2273,28 +2249,28 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>508</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -2302,28 +2278,28 @@
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>509</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
@@ -2331,28 +2307,28 @@
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>510</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -2360,28 +2336,28 @@
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
@@ -2389,28 +2365,28 @@
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>511</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
@@ -2418,28 +2394,28 @@
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>512</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
@@ -2447,28 +2423,28 @@
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -2476,28 +2452,28 @@
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -2505,28 +2481,28 @@
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>514</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
@@ -2534,28 +2510,28 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>515</v>
+        <v>99</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
         <v>12</v>
@@ -2563,28 +2539,28 @@
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
-        <v>516</v>
+        <v>106</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="I15" t="s">
         <v>12</v>
@@ -2592,28 +2568,28 @@
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>517</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I16" t="s">
         <v>12</v>
@@ -2621,28 +2597,28 @@
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>518</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I17" t="s">
         <v>12</v>
@@ -2650,28 +2626,28 @@
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G18" t="s">
-        <v>519</v>
+        <v>127</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I18" t="s">
         <v>12</v>
@@ -2679,28 +2655,28 @@
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G19" t="s">
-        <v>520</v>
+        <v>134</v>
       </c>
       <c r="H19" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="I19" t="s">
         <v>12</v>
@@ -2708,28 +2684,28 @@
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>521</v>
+        <v>141</v>
       </c>
       <c r="H20" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="I20" t="s">
         <v>12</v>
@@ -2737,28 +2713,28 @@
     </row>
     <row r="21" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="G21" t="s">
-        <v>522</v>
+        <v>148</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="I21" t="s">
         <v>12</v>
@@ -2766,28 +2742,28 @@
     </row>
     <row r="22" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="G22" t="s">
-        <v>523</v>
+        <v>155</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I22" t="s">
         <v>12</v>
@@ -2795,28 +2771,28 @@
     </row>
     <row r="23" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G23" t="s">
-        <v>524</v>
+        <v>162</v>
       </c>
       <c r="H23" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I23" t="s">
         <v>12</v>
@@ -2824,28 +2800,28 @@
     </row>
     <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F24" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="G24" t="s">
-        <v>525</v>
+        <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="I24" t="s">
         <v>12</v>
@@ -2853,28 +2829,28 @@
     </row>
     <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="F25" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="G25" t="s">
-        <v>526</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="I25" t="s">
         <v>12</v>
@@ -2882,28 +2858,28 @@
     </row>
     <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G26" t="s">
-        <v>527</v>
+        <v>182</v>
       </c>
       <c r="H26" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="I26" t="s">
         <v>12</v>
@@ -2911,28 +2887,28 @@
     </row>
     <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="G27" t="s">
-        <v>528</v>
+        <v>189</v>
       </c>
       <c r="H27" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="I27" t="s">
         <v>12</v>
@@ -2940,28 +2916,28 @@
     </row>
     <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="G28" t="s">
-        <v>529</v>
+        <v>196</v>
       </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="I28" t="s">
         <v>12</v>
@@ -2969,28 +2945,28 @@
     </row>
     <row r="29" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="G29" t="s">
-        <v>530</v>
+        <v>203</v>
       </c>
       <c r="H29" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I29" t="s">
         <v>12</v>
@@ -2998,28 +2974,28 @@
     </row>
     <row r="30" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="G30" t="s">
-        <v>531</v>
+        <v>210</v>
       </c>
       <c r="H30" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="I30" t="s">
         <v>12</v>
@@ -3027,28 +3003,28 @@
     </row>
     <row r="31" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="F31" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="G31" t="s">
-        <v>532</v>
+        <v>216</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="I31" t="s">
         <v>12</v>
@@ -3056,28 +3032,28 @@
     </row>
     <row r="32" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="F32" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="G32" t="s">
-        <v>533</v>
+        <v>223</v>
       </c>
       <c r="H32" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="I32" t="s">
         <v>12</v>
@@ -3085,28 +3061,28 @@
     </row>
     <row r="33" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="E33" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="F33" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="G33" t="s">
-        <v>534</v>
+        <v>230</v>
       </c>
       <c r="H33" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="I33" t="s">
         <v>12</v>
@@ -3114,28 +3090,28 @@
     </row>
     <row r="34" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D34" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="F34" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="G34" t="s">
-        <v>535</v>
+        <v>237</v>
       </c>
       <c r="H34" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="I34" t="s">
         <v>12</v>
@@ -3143,28 +3119,28 @@
     </row>
     <row r="35" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="F35" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="G35" t="s">
-        <v>536</v>
+        <v>244</v>
       </c>
       <c r="H35" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="I35" t="s">
         <v>12</v>
@@ -3172,28 +3148,28 @@
     </row>
     <row r="36" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="F36" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="G36" t="s">
-        <v>537</v>
+        <v>251</v>
       </c>
       <c r="H36" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="I36" t="s">
         <v>12</v>
@@ -3201,28 +3177,28 @@
     </row>
     <row r="37" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="F37" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="G37" t="s">
-        <v>538</v>
+        <v>258</v>
       </c>
       <c r="H37" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="I37" t="s">
         <v>12</v>
@@ -3230,28 +3206,28 @@
     </row>
     <row r="38" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="C38" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="F38" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="G38" t="s">
-        <v>539</v>
+        <v>265</v>
       </c>
       <c r="H38" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="I38" t="s">
         <v>12</v>
@@ -3259,28 +3235,28 @@
     </row>
     <row r="39" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="C39" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>269</v>
       </c>
       <c r="E39" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="F39" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="G39" t="s">
-        <v>540</v>
+        <v>272</v>
       </c>
       <c r="H39" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="I39" t="s">
         <v>12</v>
@@ -3288,28 +3264,28 @@
     </row>
     <row r="40" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E40" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s">
-        <v>541</v>
+        <v>279</v>
       </c>
       <c r="H40" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="I40" t="s">
         <v>12</v>
@@ -3317,28 +3293,28 @@
     </row>
     <row r="41" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="F41" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="G41" t="s">
-        <v>542</v>
+        <v>286</v>
       </c>
       <c r="H41" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="I41" t="s">
         <v>12</v>
@@ -3346,28 +3322,28 @@
     </row>
     <row r="42" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="C42" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="F42" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="G42" t="s">
-        <v>543</v>
+        <v>293</v>
       </c>
       <c r="H42" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="I42" t="s">
         <v>12</v>
@@ -3375,28 +3351,28 @@
     </row>
     <row r="43" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="F43" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="G43" t="s">
-        <v>544</v>
+        <v>300</v>
       </c>
       <c r="H43" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="I43" t="s">
         <v>12</v>
@@ -3404,28 +3380,28 @@
     </row>
     <row r="44" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="C44" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>304</v>
       </c>
       <c r="E44" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="F44" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="G44" t="s">
-        <v>545</v>
+        <v>307</v>
       </c>
       <c r="H44" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="I44" t="s">
         <v>12</v>
@@ -3433,28 +3409,28 @@
     </row>
     <row r="45" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C45" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="D45" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="F45" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="G45" t="s">
-        <v>546</v>
+        <v>315</v>
       </c>
       <c r="H45" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="I45" t="s">
         <v>12</v>
@@ -3462,28 +3438,28 @@
     </row>
     <row r="46" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="D46" t="s">
-        <v>278</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="F46" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="G46" t="s">
-        <v>547</v>
+        <v>322</v>
       </c>
       <c r="H46" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="I46" t="s">
         <v>12</v>
@@ -3491,28 +3467,28 @@
     </row>
     <row r="47" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="F47" t="s">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="G47" t="s">
-        <v>548</v>
+        <v>329</v>
       </c>
       <c r="H47" t="s">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="I47" t="s">
         <v>12</v>
@@ -3520,28 +3496,28 @@
     </row>
     <row r="48" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="C48" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>333</v>
       </c>
       <c r="E48" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="F48" t="s">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="G48" t="s">
-        <v>549</v>
+        <v>336</v>
       </c>
       <c r="H48" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="I48" t="s">
         <v>12</v>
@@ -3549,28 +3525,28 @@
     </row>
     <row r="49" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="D49" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="E49" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="F49" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="G49" t="s">
-        <v>550</v>
+        <v>343</v>
       </c>
       <c r="H49" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="I49" t="s">
         <v>12</v>
@@ -3578,28 +3554,28 @@
     </row>
     <row r="50" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>300</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="C50" t="s">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="D50" t="s">
-        <v>302</v>
+        <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="F50" t="s">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="G50" t="s">
-        <v>551</v>
+        <v>350</v>
       </c>
       <c r="H50" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="I50" t="s">
         <v>12</v>
@@ -3607,28 +3583,28 @@
     </row>
     <row r="51" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="C51" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="F51" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="G51" t="s">
-        <v>552</v>
+        <v>357</v>
       </c>
       <c r="H51" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="I51" t="s">
         <v>12</v>
@@ -3636,28 +3612,28 @@
     </row>
     <row r="52" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="C52" t="s">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="F52" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="G52" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="H52" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="I52" t="s">
         <v>12</v>
@@ -3665,28 +3641,28 @@
     </row>
     <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="C53" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="F53" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G53" t="s">
-        <v>554</v>
+        <v>371</v>
       </c>
       <c r="H53" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="I53" t="s">
         <v>12</v>
@@ -3694,28 +3670,28 @@
     </row>
     <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="C54" t="s">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="D54" t="s">
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>327</v>
+        <v>376</v>
       </c>
       <c r="F54" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="G54" t="s">
-        <v>555</v>
+        <v>378</v>
       </c>
       <c r="H54" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="I54" t="s">
         <v>12</v>
@@ -3723,28 +3699,28 @@
     </row>
     <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="C55" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="F55" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="G55" t="s">
-        <v>556</v>
+        <v>385</v>
       </c>
       <c r="H55" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="I55" t="s">
         <v>12</v>
@@ -3752,28 +3728,28 @@
     </row>
     <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="C56" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="F56" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="G56" t="s">
-        <v>557</v>
+        <v>392</v>
       </c>
       <c r="H56" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="I56" t="s">
         <v>12</v>
@@ -3781,28 +3757,28 @@
     </row>
     <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="C57" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>397</v>
       </c>
       <c r="E57" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="F57" t="s">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="G57" t="s">
-        <v>558</v>
+        <v>400</v>
       </c>
       <c r="H57" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="I57" t="s">
         <v>12</v>
@@ -3810,28 +3786,28 @@
     </row>
     <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="C58" t="s">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="D58" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="F58" t="s">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="G58" t="s">
-        <v>559</v>
+        <v>407</v>
       </c>
       <c r="H58" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="I58" t="s">
         <v>12</v>
@@ -3839,28 +3815,28 @@
     </row>
     <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>355</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="C59" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="D59" t="s">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F59" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="G59" t="s">
-        <v>560</v>
+        <v>413</v>
       </c>
       <c r="H59" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="I59" t="s">
         <v>12</v>
@@ -3868,28 +3844,28 @@
     </row>
     <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
       <c r="C60" t="s">
-        <v>362</v>
+        <v>416</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>417</v>
       </c>
       <c r="E60" t="s">
-        <v>363</v>
+        <v>418</v>
       </c>
       <c r="F60" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="G60" t="s">
-        <v>561</v>
+        <v>420</v>
       </c>
       <c r="H60" t="s">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="I60" t="s">
         <v>12</v>
@@ -3897,28 +3873,28 @@
     </row>
     <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>366</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="C61" t="s">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="D61" t="s">
-        <v>368</v>
+        <v>424</v>
       </c>
       <c r="E61" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="F61" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="G61" t="s">
-        <v>562</v>
+        <v>427</v>
       </c>
       <c r="H61" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="I61" t="s">
         <v>12</v>
@@ -3926,28 +3902,28 @@
     </row>
     <row r="62" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="B62" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C62" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
       <c r="D62" t="s">
-        <v>374</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="F62" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="G62" t="s">
-        <v>563</v>
+        <v>434</v>
       </c>
       <c r="H62" t="s">
-        <v>377</v>
+        <v>435</v>
       </c>
       <c r="I62" t="s">
         <v>12</v>
@@ -3955,28 +3931,28 @@
     </row>
     <row r="63" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="C63" t="s">
-        <v>380</v>
+        <v>438</v>
       </c>
       <c r="D63" t="s">
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="F63" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="G63" t="s">
-        <v>564</v>
+        <v>441</v>
       </c>
       <c r="H63" t="s">
-        <v>383</v>
+        <v>442</v>
       </c>
       <c r="I63" t="s">
         <v>12</v>
@@ -3984,28 +3960,28 @@
     </row>
     <row r="64" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="C64" t="s">
-        <v>386</v>
+        <v>445</v>
       </c>
       <c r="D64" t="s">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>387</v>
+        <v>446</v>
       </c>
       <c r="F64" t="s">
-        <v>388</v>
+        <v>447</v>
       </c>
       <c r="G64" t="s">
-        <v>565</v>
+        <v>448</v>
       </c>
       <c r="H64" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="I64" t="s">
         <v>12</v>
@@ -4013,28 +3989,28 @@
     </row>
     <row r="65" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="C65" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="F65" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="G65" t="s">
-        <v>566</v>
+        <v>455</v>
       </c>
       <c r="H65" t="s">
-        <v>395</v>
+        <v>456</v>
       </c>
       <c r="I65" t="s">
         <v>12</v>
@@ -4042,28 +4018,28 @@
     </row>
     <row r="66" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s">
-        <v>397</v>
+        <v>458</v>
       </c>
       <c r="C66" t="s">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="D66" t="s">
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>399</v>
+        <v>460</v>
       </c>
       <c r="F66" t="s">
-        <v>400</v>
+        <v>461</v>
       </c>
       <c r="G66" t="s">
-        <v>567</v>
+        <v>462</v>
       </c>
       <c r="H66" t="s">
-        <v>401</v>
+        <v>463</v>
       </c>
       <c r="I66" t="s">
         <v>12</v>
@@ -4071,28 +4047,28 @@
     </row>
     <row r="67" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s">
-        <v>403</v>
+        <v>465</v>
       </c>
       <c r="C67" t="s">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="D67" t="s">
-        <v>12</v>
+        <v>466</v>
       </c>
       <c r="E67" t="s">
-        <v>405</v>
+        <v>467</v>
       </c>
       <c r="F67" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="G67" t="s">
-        <v>568</v>
+        <v>469</v>
       </c>
       <c r="H67" t="s">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="I67" t="s">
         <v>12</v>
@@ -4100,28 +4076,28 @@
     </row>
     <row r="68" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>408</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="C68" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="D68" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
       <c r="E68" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="F68" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="G68" t="s">
-        <v>569</v>
+        <v>477</v>
       </c>
       <c r="H68" t="s">
-        <v>413</v>
+        <v>478</v>
       </c>
       <c r="I68" t="s">
         <v>12</v>
@@ -4129,28 +4105,28 @@
     </row>
     <row r="69" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>414</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="C69" t="s">
-        <v>416</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s">
-        <v>417</v>
+        <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="F69" t="s">
-        <v>419</v>
+        <v>483</v>
       </c>
       <c r="G69" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="H69" t="s">
-        <v>420</v>
+        <v>485</v>
       </c>
       <c r="I69" t="s">
         <v>12</v>
@@ -4158,28 +4134,28 @@
     </row>
     <row r="70" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>421</v>
+        <v>486</v>
       </c>
       <c r="B70" t="s">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C70" t="s">
-        <v>423</v>
+        <v>488</v>
       </c>
       <c r="D70" t="s">
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>424</v>
+        <v>489</v>
       </c>
       <c r="F70" t="s">
-        <v>425</v>
+        <v>490</v>
       </c>
       <c r="G70" t="s">
-        <v>571</v>
+        <v>491</v>
       </c>
       <c r="H70" t="s">
-        <v>426</v>
+        <v>492</v>
       </c>
       <c r="I70" t="s">
         <v>12</v>
@@ -4187,28 +4163,28 @@
     </row>
     <row r="71" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="B71" t="s">
-        <v>428</v>
+        <v>494</v>
       </c>
       <c r="C71" t="s">
-        <v>429</v>
+        <v>495</v>
       </c>
       <c r="D71" t="s">
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>430</v>
+        <v>496</v>
       </c>
       <c r="F71" t="s">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="G71" t="s">
-        <v>572</v>
+        <v>498</v>
       </c>
       <c r="H71" t="s">
-        <v>432</v>
+        <v>499</v>
       </c>
       <c r="I71" t="s">
         <v>12</v>
@@ -4216,28 +4192,28 @@
     </row>
     <row r="72" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="B72" t="s">
-        <v>434</v>
+        <v>501</v>
       </c>
       <c r="C72" t="s">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
       <c r="F72" t="s">
-        <v>437</v>
+        <v>504</v>
       </c>
       <c r="G72" t="s">
-        <v>573</v>
+        <v>505</v>
       </c>
       <c r="H72" t="s">
-        <v>438</v>
+        <v>506</v>
       </c>
       <c r="I72" t="s">
         <v>12</v>
@@ -4245,28 +4221,28 @@
     </row>
     <row r="73" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s">
-        <v>440</v>
+        <v>508</v>
       </c>
       <c r="C73" t="s">
-        <v>441</v>
+        <v>509</v>
       </c>
       <c r="D73" t="s">
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>442</v>
+        <v>510</v>
       </c>
       <c r="F73" t="s">
-        <v>443</v>
+        <v>511</v>
       </c>
       <c r="G73" t="s">
-        <v>574</v>
+        <v>512</v>
       </c>
       <c r="H73" t="s">
-        <v>444</v>
+        <v>513</v>
       </c>
       <c r="I73" t="s">
         <v>12</v>
@@ -4274,28 +4250,28 @@
     </row>
     <row r="74" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>445</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="C74" t="s">
-        <v>447</v>
+        <v>516</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>517</v>
       </c>
       <c r="E74" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="F74" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="G74" t="s">
-        <v>575</v>
+        <v>520</v>
       </c>
       <c r="H74" t="s">
-        <v>450</v>
+        <v>521</v>
       </c>
       <c r="I74" t="s">
         <v>12</v>
@@ -4303,28 +4279,28 @@
     </row>
     <row r="75" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s">
-        <v>452</v>
+        <v>523</v>
       </c>
       <c r="C75" t="s">
-        <v>453</v>
+        <v>524</v>
       </c>
       <c r="D75" t="s">
-        <v>454</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>455</v>
+        <v>525</v>
       </c>
       <c r="F75" t="s">
-        <v>456</v>
+        <v>526</v>
       </c>
       <c r="G75" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="H75" t="s">
-        <v>457</v>
+        <v>528</v>
       </c>
       <c r="I75" t="s">
         <v>12</v>
@@ -4332,28 +4308,28 @@
     </row>
     <row r="76" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>458</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s">
-        <v>459</v>
+        <v>530</v>
       </c>
       <c r="C76" t="s">
-        <v>460</v>
+        <v>531</v>
       </c>
       <c r="D76" t="s">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>461</v>
+        <v>532</v>
       </c>
       <c r="F76" t="s">
-        <v>462</v>
+        <v>533</v>
       </c>
       <c r="G76" t="s">
-        <v>577</v>
+        <v>534</v>
       </c>
       <c r="H76" t="s">
-        <v>463</v>
+        <v>535</v>
       </c>
       <c r="I76" t="s">
         <v>12</v>
@@ -4361,28 +4337,28 @@
     </row>
     <row r="77" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="B77" t="s">
-        <v>465</v>
+        <v>537</v>
       </c>
       <c r="C77" t="s">
-        <v>466</v>
+        <v>538</v>
       </c>
       <c r="D77" t="s">
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>467</v>
+        <v>539</v>
       </c>
       <c r="F77" t="s">
-        <v>468</v>
+        <v>540</v>
       </c>
       <c r="G77" t="s">
-        <v>578</v>
+        <v>541</v>
       </c>
       <c r="H77" t="s">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="I77" t="s">
         <v>12</v>
@@ -4390,28 +4366,28 @@
     </row>
     <row r="78" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>470</v>
+        <v>543</v>
       </c>
       <c r="B78" t="s">
-        <v>471</v>
+        <v>544</v>
       </c>
       <c r="C78" t="s">
-        <v>472</v>
+        <v>545</v>
       </c>
       <c r="D78" t="s">
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>473</v>
+        <v>546</v>
       </c>
       <c r="F78" t="s">
-        <v>474</v>
+        <v>547</v>
       </c>
       <c r="G78" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="H78" t="s">
-        <v>475</v>
+        <v>549</v>
       </c>
       <c r="I78" t="s">
         <v>12</v>
@@ -4419,28 +4395,28 @@
     </row>
     <row r="79" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>476</v>
+        <v>550</v>
       </c>
       <c r="B79" t="s">
-        <v>477</v>
+        <v>551</v>
       </c>
       <c r="C79" t="s">
-        <v>478</v>
+        <v>551</v>
       </c>
       <c r="D79" t="s">
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="F79" t="s">
-        <v>480</v>
+        <v>553</v>
       </c>
       <c r="G79" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="H79" t="s">
-        <v>481</v>
+        <v>555</v>
       </c>
       <c r="I79" t="s">
         <v>12</v>
@@ -4448,28 +4424,28 @@
     </row>
     <row r="80" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>482</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s">
-        <v>483</v>
+        <v>557</v>
       </c>
       <c r="C80" t="s">
-        <v>483</v>
+        <v>558</v>
       </c>
       <c r="D80" t="s">
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>484</v>
+        <v>559</v>
       </c>
       <c r="F80" t="s">
-        <v>485</v>
+        <v>560</v>
       </c>
       <c r="G80" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="H80" t="s">
-        <v>486</v>
+        <v>562</v>
       </c>
       <c r="I80" t="s">
         <v>12</v>
@@ -4477,28 +4453,28 @@
     </row>
     <row r="81" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>487</v>
+        <v>563</v>
       </c>
       <c r="B81" t="s">
-        <v>488</v>
+        <v>564</v>
       </c>
       <c r="C81" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="D81" t="s">
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>490</v>
+        <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>491</v>
+        <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>492</v>
+        <v>566</v>
       </c>
       <c r="H81" t="s">
-        <v>493</v>
+        <v>567</v>
       </c>
       <c r="I81" t="s">
         <v>12</v>
@@ -4506,59 +4482,30 @@
     </row>
     <row r="82" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>494</v>
+        <v>568</v>
       </c>
       <c r="B82" t="s">
-        <v>495</v>
+        <v>569</v>
       </c>
       <c r="C82" t="s">
-        <v>496</v>
+        <v>570</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>12</v>
+        <v>571</v>
       </c>
       <c r="F82" t="s">
-        <v>12</v>
+        <v>572</v>
       </c>
       <c r="G82" t="s">
-        <v>497</v>
+        <v>573</v>
       </c>
       <c r="H82" t="s">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="I82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>499</v>
-      </c>
-      <c r="B83" t="s">
-        <v>500</v>
-      </c>
-      <c r="C83" t="s">
-        <v>501</v>
-      </c>
-      <c r="D83" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" t="s">
-        <v>502</v>
-      </c>
-      <c r="F83" t="s">
-        <v>503</v>
-      </c>
-      <c r="G83" t="s">
-        <v>504</v>
-      </c>
-      <c r="H83" t="s">
-        <v>505</v>
-      </c>
-      <c r="I83" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4566,7 +4513,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I2 A8:I8 A3:F3 H3:I3 A4:F4 H4:I4 A5:F5 H5:I5 A6:F6 H6:I6 A7:F7 H7:I7 A12:I12 A9:F9 H9:I9 A10:F10 H10:I10 A11:F11 H11:I11 A81:I83 A13:F13 H13:I13 A14:F14 H14:I14 A15:F15 H15:I15 A16:F16 H16:I16 A17:F17 H17:I17 A18:F18 H18:I18 A19:F19 H19:I19 A20:F20 H20:I20 A21:F21 H21:I21 A22:F22 H22:I22 A23:F23 H23:I23 A24:F24 H24:I24 A25:F25 H25:I25 A26:F26 H26:I26 A27:F27 H27:I27 A28:F28 H28:I28 A29:F29 H29:I29 A30:F30 H30:I30 A31:F31 H31:I31 A32:F32 H32:I32 A33:F33 H33:I33 A34:F34 H34:I34 A35:F35 H35:I35 A36:F36 H36:I36 A37:F37 H37:I37 A38:F38 H38:I38 A39:F39 H39:I39 A40:F40 H40:I40 A41:F41 H41:I41 A42:F42 H42:I42 A43:F43 H43:I43 A44:F44 H44:I44 A45:F45 H45:I45 A46:F46 H46:I46 A47:F47 H47:I47 A48:F48 H48:I48 A49:F49 H49:I49 A50:F50 H50:I50 A51:F51 H51:I51 A52:F52 H52:I52 A53:F53 H53:I53 A54:F54 H54:I54 A55:F55 H55:I55 A56:F56 H56:I56 A57:F57 H57:I57 A58:F58 H58:I58 A59:F59 H59:I59 A60:F60 H60:I60 A61:F61 H61:I61 A62:F62 H62:I62 A63:F63 H63:I63 A64:F64 H64:I64 A65:F65 H65:I65 A66:F66 H66:I66 A67:F67 H67:I67 A68:F68 H68:I68 A69:F69 H69:I69 A70:F70 H70:I70 A71:F71 H71:I71 A72:F72 H72:I72 A73:F73 H73:I73 A74:F74 H74:I74 A75:F75 H75:I75 A76:F76 H76:I76 A77:F77 H77:I77 A78:F78 H78:I78 A79:F79 H79:I79 A80:F80 H80:I80" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I26 A27:I82" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>